--- a/rl_env/outputs/rule_based_baseline.xlsx
+++ b/rl_env/outputs/rule_based_baseline.xlsx
@@ -469,13 +469,13 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4830436</v>
+        <v>0.56722546</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.0113295615</v>
+        <v>-0.108633965</v>
       </c>
     </row>
     <row r="3">
@@ -486,13 +486,13 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>0.47171405</v>
+        <v>0.4585915</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0113295615</v>
+        <v>0.108633965</v>
       </c>
     </row>
     <row r="4">
@@ -503,13 +503,13 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4830436</v>
+        <v>0.56722546</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0113295615</v>
+        <v>-0.108633965</v>
       </c>
     </row>
     <row r="5">
@@ -520,13 +520,13 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>0.47171405</v>
+        <v>0.4585915</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.21048835</v>
+        <v>-0.15216494</v>
       </c>
     </row>
     <row r="6">
@@ -537,7 +537,7 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2612257</v>
+        <v>0.30642655</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -554,13 +554,13 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2612257</v>
+        <v>0.30642655</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0005713701</v>
+        <v>-0.0025253892</v>
       </c>
     </row>
     <row r="8">
@@ -571,13 +571,13 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>0.26179707</v>
+        <v>0.30390117</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>0.005543649</v>
       </c>
     </row>
     <row r="9">
@@ -588,13 +588,13 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>0.26179707</v>
+        <v>0.30944481</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0026104152</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -605,7 +605,7 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2644075</v>
+        <v>0.30944481</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -622,13 +622,13 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2644075</v>
+        <v>0.30944481</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.01954633</v>
+        <v>-0.025866508</v>
       </c>
     </row>
     <row r="12">
@@ -639,13 +639,13 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>0.24486116</v>
+        <v>0.2835783</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0.01709953</v>
+        <v>0.02883327</v>
       </c>
     </row>
     <row r="13">
@@ -656,13 +656,13 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2619607</v>
+        <v>0.31241158</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.009556650999999999</v>
+        <v>-0.023329884</v>
       </c>
     </row>
     <row r="14">
@@ -673,13 +673,13 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>0.25240403</v>
+        <v>0.2890817</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>2.8043985e-05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -690,13 +690,13 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>0.25243208</v>
+        <v>0.2890817</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0.00045970082</v>
+        <v>-0.0023734272</v>
       </c>
     </row>
     <row r="16">
@@ -707,7 +707,7 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>0.25289178</v>
+        <v>0.28670827</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -724,13 +724,13 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>0.25289178</v>
+        <v>0.28670827</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0.004316002</v>
+        <v>0.0027720928</v>
       </c>
     </row>
     <row r="18">
@@ -741,7 +741,7 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>0.25720778</v>
+        <v>0.28948036</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -758,7 +758,7 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>0.25720778</v>
+        <v>0.28948036</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -775,13 +775,13 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>0.25720778</v>
+        <v>0.28948036</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>0.0059405565</v>
       </c>
     </row>
     <row r="21">
@@ -792,13 +792,13 @@
         <v>20</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>0.25720778</v>
+        <v>0.2954209</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>-0.002238214</v>
+        <v>-0.04831313</v>
       </c>
     </row>
     <row r="22">
@@ -809,13 +809,13 @@
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>0.25496957</v>
+        <v>0.2971078</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>-0.0049382746</v>
       </c>
     </row>
     <row r="23">
@@ -826,7 +826,7 @@
         <v>2</v>
       </c>
       <c r="C23" t="n">
-        <v>0.25496957</v>
+        <v>0.2921695</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -843,7 +843,7 @@
         <v>3</v>
       </c>
       <c r="C24" t="n">
-        <v>0.25496957</v>
+        <v>0.2921695</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -860,7 +860,7 @@
         <v>4</v>
       </c>
       <c r="C25" t="n">
-        <v>0.25496957</v>
+        <v>0.2921695</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -877,7 +877,7 @@
         <v>5</v>
       </c>
       <c r="C26" t="n">
-        <v>0.25496957</v>
+        <v>0.2921695</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -894,13 +894,13 @@
         <v>6</v>
       </c>
       <c r="C27" t="n">
-        <v>0.25496957</v>
+        <v>0.2921695</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0027749538</v>
+        <v>-0.002456963</v>
       </c>
     </row>
     <row r="28">
@@ -911,13 +911,13 @@
         <v>7</v>
       </c>
       <c r="C28" t="n">
-        <v>0.25774452</v>
+        <v>0.28971255</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>0.005394578</v>
       </c>
     </row>
     <row r="29">
@@ -928,13 +928,13 @@
         <v>8</v>
       </c>
       <c r="C29" t="n">
-        <v>0.25774452</v>
+        <v>0.29510713</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.0010299385</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -945,13 +945,13 @@
         <v>9</v>
       </c>
       <c r="C30" t="n">
-        <v>0.25671458</v>
+        <v>0.29510713</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>-0.003129065</v>
       </c>
     </row>
     <row r="31">
@@ -962,7 +962,7 @@
         <v>10</v>
       </c>
       <c r="C31" t="n">
-        <v>0.25671458</v>
+        <v>0.29197806</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
@@ -979,7 +979,7 @@
         <v>11</v>
       </c>
       <c r="C32" t="n">
-        <v>0.25671458</v>
+        <v>0.29197806</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
@@ -996,13 +996,13 @@
         <v>12</v>
       </c>
       <c r="C33" t="n">
-        <v>0.25671458</v>
+        <v>0.29197806</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>0.0027124286</v>
       </c>
     </row>
     <row r="34">
@@ -1013,13 +1013,13 @@
         <v>13</v>
       </c>
       <c r="C34" t="n">
-        <v>0.25671458</v>
+        <v>0.2946905</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>2.8342009e-05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -1030,13 +1030,13 @@
         <v>14</v>
       </c>
       <c r="C35" t="n">
-        <v>0.25674292</v>
+        <v>0.2946905</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>0.00046485662</v>
+        <v>-0.0024005473</v>
       </c>
     </row>
     <row r="36">
@@ -1047,13 +1047,13 @@
         <v>15</v>
       </c>
       <c r="C36" t="n">
-        <v>0.25720778</v>
+        <v>0.29228994</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>0.33300027</v>
+        <v>0.27634707</v>
       </c>
     </row>
     <row r="37">
@@ -1064,13 +1064,13 @@
         <v>16</v>
       </c>
       <c r="C37" t="n">
-        <v>0.59020805</v>
+        <v>0.5686369999999999</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.33291247</v>
+        <v>-0.28391653</v>
       </c>
     </row>
     <row r="38">
@@ -1081,13 +1081,13 @@
         <v>17</v>
       </c>
       <c r="C38" t="n">
-        <v>0.25729558</v>
+        <v>0.28472048</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>-8.779764e-05</v>
+        <v>0.010700434</v>
       </c>
     </row>
     <row r="39">
@@ -1098,13 +1098,13 @@
         <v>18</v>
       </c>
       <c r="C39" t="n">
-        <v>0.25720778</v>
+        <v>0.2954209</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>0.0048542917</v>
+        <v>-0.00064122677</v>
       </c>
     </row>
     <row r="40">
@@ -1115,13 +1115,13 @@
         <v>19</v>
       </c>
       <c r="C40" t="n">
-        <v>0.26206207</v>
+        <v>0.2947797</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>0.029737264</v>
+        <v>0.09383899</v>
       </c>
     </row>
     <row r="41">
@@ -1132,13 +1132,13 @@
         <v>20</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>0.29179934</v>
+        <v>0.38861868</v>
       </c>
       <c r="D41" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>-0.03682977</v>
+        <v>-0.14465229</v>
       </c>
     </row>
     <row r="42">
@@ -1149,13 +1149,13 @@
         <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>0.25496957</v>
+        <v>0.29396638</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>-0.0049075484</v>
       </c>
     </row>
     <row r="43">
@@ -1166,7 +1166,7 @@
         <v>2</v>
       </c>
       <c r="C43" t="n">
-        <v>0.25496957</v>
+        <v>0.28905883</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
@@ -1183,7 +1183,7 @@
         <v>3</v>
       </c>
       <c r="C44" t="n">
-        <v>0.25496957</v>
+        <v>0.28905883</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
@@ -1200,7 +1200,7 @@
         <v>4</v>
       </c>
       <c r="C45" t="n">
-        <v>0.25496957</v>
+        <v>0.28905883</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
@@ -1217,7 +1217,7 @@
         <v>5</v>
       </c>
       <c r="C46" t="n">
-        <v>0.25496957</v>
+        <v>0.28905883</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
@@ -1234,13 +1234,13 @@
         <v>6</v>
       </c>
       <c r="C47" t="n">
-        <v>0.25496957</v>
+        <v>0.28905883</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>0.0027749538</v>
+        <v>-0.0024413764</v>
       </c>
     </row>
     <row r="48">
@@ -1251,13 +1251,13 @@
         <v>7</v>
       </c>
       <c r="C48" t="n">
-        <v>0.25774452</v>
+        <v>0.28661746</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>0.0053606033</v>
       </c>
     </row>
     <row r="49">
@@ -1268,13 +1268,13 @@
         <v>8</v>
       </c>
       <c r="C49" t="n">
-        <v>0.25774452</v>
+        <v>0.29197806</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.0010299385</v>
+        <v>0.003129065</v>
       </c>
     </row>
     <row r="50">
@@ -1285,7 +1285,7 @@
         <v>9</v>
       </c>
       <c r="C50" t="n">
-        <v>0.25671458</v>
+        <v>0.29510713</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -1302,7 +1302,7 @@
         <v>10</v>
       </c>
       <c r="C51" t="n">
-        <v>0.25671458</v>
+        <v>0.29510713</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
@@ -1319,13 +1319,13 @@
         <v>11</v>
       </c>
       <c r="C52" t="n">
-        <v>0.25671458</v>
+        <v>0.29510713</v>
       </c>
       <c r="D52" t="n">
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>-0.003129065</v>
       </c>
     </row>
     <row r="53">
@@ -1336,13 +1336,13 @@
         <v>12</v>
       </c>
       <c r="C53" t="n">
-        <v>0.25671458</v>
+        <v>0.29197806</v>
       </c>
       <c r="D53" t="n">
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>0.0027124286</v>
       </c>
     </row>
     <row r="54">
@@ -1353,13 +1353,13 @@
         <v>13</v>
       </c>
       <c r="C54" t="n">
-        <v>0.25671458</v>
+        <v>0.2946905</v>
       </c>
       <c r="D54" t="n">
         <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>2.8342009e-05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -1370,13 +1370,13 @@
         <v>14</v>
       </c>
       <c r="C55" t="n">
-        <v>0.25674292</v>
+        <v>0.2946905</v>
       </c>
       <c r="D55" t="n">
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>0.00046485662</v>
+        <v>-0.0024005473</v>
       </c>
     </row>
     <row r="56">
@@ -1387,7 +1387,7 @@
         <v>15</v>
       </c>
       <c r="C56" t="n">
-        <v>0.25720778</v>
+        <v>0.29228994</v>
       </c>
       <c r="D56" t="n">
         <v>0</v>
@@ -1404,7 +1404,7 @@
         <v>16</v>
       </c>
       <c r="C57" t="n">
-        <v>0.25720778</v>
+        <v>0.29228994</v>
       </c>
       <c r="D57" t="n">
         <v>0</v>
@@ -1421,7 +1421,7 @@
         <v>17</v>
       </c>
       <c r="C58" t="n">
-        <v>0.25720778</v>
+        <v>0.29228994</v>
       </c>
       <c r="D58" t="n">
         <v>0</v>
@@ -1438,7 +1438,7 @@
         <v>18</v>
       </c>
       <c r="C59" t="n">
-        <v>0.25720778</v>
+        <v>0.29228994</v>
       </c>
       <c r="D59" t="n">
         <v>0</v>
@@ -1455,7 +1455,7 @@
         <v>19</v>
       </c>
       <c r="C60" t="n">
-        <v>0.25720778</v>
+        <v>0.29228994</v>
       </c>
       <c r="D60" t="n">
         <v>0</v>
@@ -1472,13 +1472,13 @@
         <v>20</v>
       </c>
       <c r="C61" s="2" t="n">
-        <v>0.25720778</v>
+        <v>0.29228994</v>
       </c>
       <c r="D61" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>-0.002238214</v>
+        <v>-0.04832356</v>
       </c>
     </row>
     <row r="62">
@@ -1489,13 +1489,13 @@
         <v>1</v>
       </c>
       <c r="C62" t="n">
-        <v>0.25496957</v>
+        <v>0.29396638</v>
       </c>
       <c r="D62" t="n">
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>0</v>
+        <v>-0.0049075484</v>
       </c>
     </row>
     <row r="63">
@@ -1506,7 +1506,7 @@
         <v>2</v>
       </c>
       <c r="C63" t="n">
-        <v>0.25496957</v>
+        <v>0.28905883</v>
       </c>
       <c r="D63" t="n">
         <v>0</v>
@@ -1523,7 +1523,7 @@
         <v>3</v>
       </c>
       <c r="C64" t="n">
-        <v>0.25496957</v>
+        <v>0.28905883</v>
       </c>
       <c r="D64" t="n">
         <v>0</v>
@@ -1540,13 +1540,13 @@
         <v>4</v>
       </c>
       <c r="C65" t="n">
-        <v>0.25496957</v>
+        <v>0.28905883</v>
       </c>
       <c r="D65" t="n">
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>0.049946398</v>
+        <v>0.117949665</v>
       </c>
     </row>
     <row r="66">
@@ -1557,13 +1557,13 @@
         <v>5</v>
       </c>
       <c r="C66" t="n">
-        <v>0.30491596</v>
+        <v>0.4070085</v>
       </c>
       <c r="D66" t="n">
         <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.0046113133</v>
+        <v>-0.04965973</v>
       </c>
     </row>
     <row r="67">
@@ -1574,13 +1574,13 @@
         <v>6</v>
       </c>
       <c r="C67" t="n">
-        <v>0.30030465</v>
+        <v>0.35734877</v>
       </c>
       <c r="D67" t="n">
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>0.007133454</v>
+        <v>0.05311361</v>
       </c>
     </row>
     <row r="68">
@@ -1591,13 +1591,13 @@
         <v>7</v>
       </c>
       <c r="C68" t="n">
-        <v>0.3074381</v>
+        <v>0.41046238</v>
       </c>
       <c r="D68" t="n">
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>0.01630029</v>
+        <v>0.007902354</v>
       </c>
     </row>
     <row r="69">
@@ -1608,13 +1608,13 @@
         <v>8</v>
       </c>
       <c r="C69" t="n">
-        <v>0.3237384</v>
+        <v>0.41836473</v>
       </c>
       <c r="D69" t="n">
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>0.022714585</v>
+        <v>0.14787152</v>
       </c>
     </row>
     <row r="70">
@@ -1625,13 +1625,13 @@
         <v>9</v>
       </c>
       <c r="C70" t="n">
-        <v>0.34645298</v>
+        <v>0.56623626</v>
       </c>
       <c r="D70" t="n">
         <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.023893654</v>
+        <v>-0.15811041</v>
       </c>
     </row>
     <row r="71">
@@ -1642,13 +1642,13 @@
         <v>10</v>
       </c>
       <c r="C71" t="n">
-        <v>0.32255933</v>
+        <v>0.40812585</v>
       </c>
       <c r="D71" t="n">
         <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.021314919</v>
+        <v>-0.033866853</v>
       </c>
     </row>
     <row r="72">
@@ -1659,13 +1659,13 @@
         <v>11</v>
       </c>
       <c r="C72" t="n">
-        <v>0.3012444</v>
+        <v>0.374259</v>
       </c>
       <c r="D72" t="n">
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>0.019929498</v>
+        <v>0.036837727</v>
       </c>
     </row>
     <row r="73">
@@ -1676,13 +1676,13 @@
         <v>12</v>
       </c>
       <c r="C73" t="n">
-        <v>0.3211739</v>
+        <v>0.41109672</v>
       </c>
       <c r="D73" t="n">
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>-0.019929498</v>
+        <v>-0.033768296</v>
       </c>
     </row>
     <row r="74">
@@ -1693,13 +1693,13 @@
         <v>13</v>
       </c>
       <c r="C74" t="n">
-        <v>0.3012444</v>
+        <v>0.37732843</v>
       </c>
       <c r="D74" t="n">
         <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>3.1262636e-05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -1710,13 +1710,13 @@
         <v>14</v>
       </c>
       <c r="C75" t="n">
-        <v>0.30127567</v>
+        <v>0.37732843</v>
       </c>
       <c r="D75" t="n">
         <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>0.00051277876</v>
+        <v>-0.0027161837</v>
       </c>
     </row>
     <row r="76">
@@ -1727,13 +1727,13 @@
         <v>15</v>
       </c>
       <c r="C76" t="n">
-        <v>0.30178845</v>
+        <v>0.37461224</v>
       </c>
       <c r="D76" t="n">
         <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>0.01475054</v>
+        <v>0.03354788</v>
       </c>
     </row>
     <row r="77">
@@ -1744,13 +1744,13 @@
         <v>16</v>
       </c>
       <c r="C77" t="n">
-        <v>0.316539</v>
+        <v>0.40816012</v>
       </c>
       <c r="D77" t="n">
         <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>-0.01475054</v>
+        <v>-0.03354788</v>
       </c>
     </row>
     <row r="78">
@@ -1761,7 +1761,7 @@
         <v>17</v>
       </c>
       <c r="C78" t="n">
-        <v>0.30178845</v>
+        <v>0.37461224</v>
       </c>
       <c r="D78" t="n">
         <v>0</v>
@@ -1778,13 +1778,13 @@
         <v>18</v>
       </c>
       <c r="C79" t="n">
-        <v>0.30178845</v>
+        <v>0.37461224</v>
       </c>
       <c r="D79" t="n">
         <v>0</v>
       </c>
       <c r="E79" t="n">
-        <v>0.008776426</v>
+        <v>0.017582446</v>
       </c>
     </row>
     <row r="80">
@@ -1795,13 +1795,13 @@
         <v>19</v>
       </c>
       <c r="C80" t="n">
-        <v>0.31056488</v>
+        <v>0.3921947</v>
       </c>
       <c r="D80" t="n">
         <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>0.32981867</v>
+        <v>0.1791591</v>
       </c>
     </row>
     <row r="81">
@@ -1812,13 +1812,13 @@
         <v>20</v>
       </c>
       <c r="C81" s="2" t="n">
-        <v>0.64038354</v>
+        <v>0.5713538</v>
       </c>
       <c r="D81" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>-0.32942134</v>
+        <v>-0.34218067</v>
       </c>
     </row>
     <row r="82">
@@ -1829,13 +1829,13 @@
         <v>1</v>
       </c>
       <c r="C82" t="n">
-        <v>0.3109622</v>
+        <v>0.27917314</v>
       </c>
       <c r="D82" t="n">
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>0.27580196</v>
+        <v>0.28049064</v>
       </c>
     </row>
     <row r="83">
@@ -1846,13 +1846,13 @@
         <v>2</v>
       </c>
       <c r="C83" t="n">
-        <v>0.58676416</v>
+        <v>0.5596638</v>
       </c>
       <c r="D83" t="n">
         <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>-0.014094114</v>
+        <v>-0.031781137</v>
       </c>
     </row>
     <row r="84">
@@ -1863,13 +1863,13 @@
         <v>3</v>
       </c>
       <c r="C84" t="n">
-        <v>0.57267004</v>
+        <v>0.52788264</v>
       </c>
       <c r="D84" t="n">
         <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>0.11731231</v>
+        <v>0.08550136999999999</v>
       </c>
     </row>
     <row r="85">
@@ -1880,13 +1880,13 @@
         <v>4</v>
       </c>
       <c r="C85" t="n">
-        <v>0.68998235</v>
+        <v>0.613384</v>
       </c>
       <c r="D85" t="n">
         <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>-0.12995815</v>
+        <v>-0.1587869</v>
       </c>
     </row>
     <row r="86">
@@ -1897,13 +1897,13 @@
         <v>5</v>
       </c>
       <c r="C86" t="n">
-        <v>0.5600242</v>
+        <v>0.45459712</v>
       </c>
       <c r="D86" t="n">
         <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>-0.003975749</v>
+        <v>-0.04869196</v>
       </c>
     </row>
     <row r="87">
@@ -1914,13 +1914,13 @@
         <v>6</v>
       </c>
       <c r="C87" t="n">
-        <v>0.55604845</v>
+        <v>0.40590516</v>
       </c>
       <c r="D87" t="n">
         <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>0.03097874</v>
+        <v>0.1494259</v>
       </c>
     </row>
     <row r="88">
@@ -1931,13 +1931,13 @@
         <v>7</v>
       </c>
       <c r="C88" t="n">
-        <v>0.5870272</v>
+        <v>0.55533105</v>
       </c>
       <c r="D88" t="n">
         <v>0</v>
       </c>
       <c r="E88" t="n">
-        <v>-0.01040417</v>
+        <v>-0.036104858</v>
       </c>
     </row>
     <row r="89">
@@ -1948,13 +1948,13 @@
         <v>8</v>
       </c>
       <c r="C89" t="n">
-        <v>0.576623</v>
+        <v>0.5192262</v>
       </c>
       <c r="D89" t="n">
         <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>-0.021902204</v>
+        <v>-0.11359179</v>
       </c>
     </row>
     <row r="90">
@@ -1965,13 +1965,13 @@
         <v>9</v>
       </c>
       <c r="C90" t="n">
-        <v>0.5547208</v>
+        <v>0.4056344</v>
       </c>
       <c r="D90" t="n">
         <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>-0.25314075</v>
+        <v>-0.029948145</v>
       </c>
     </row>
     <row r="91">
@@ -1982,13 +1982,13 @@
         <v>10</v>
       </c>
       <c r="C91" t="n">
-        <v>0.30158007</v>
+        <v>0.37568626</v>
       </c>
       <c r="D91" t="n">
         <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>0.0018106401</v>
+        <v>-0.00353235</v>
       </c>
     </row>
     <row r="92">
@@ -1999,7 +1999,7 @@
         <v>11</v>
       </c>
       <c r="C92" t="n">
-        <v>0.3033907</v>
+        <v>0.3721539</v>
       </c>
       <c r="D92" t="n">
         <v>0</v>
@@ -2016,13 +2016,13 @@
         <v>12</v>
       </c>
       <c r="C93" t="n">
-        <v>0.3033907</v>
+        <v>0.3721539</v>
       </c>
       <c r="D93" t="n">
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>-0.00033679605</v>
+        <v>-0.00199759</v>
       </c>
     </row>
     <row r="94">
@@ -2033,13 +2033,13 @@
         <v>13</v>
       </c>
       <c r="C94" t="n">
-        <v>0.30305392</v>
+        <v>0.37015632</v>
       </c>
       <c r="D94" t="n">
         <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>0.018252999</v>
+        <v>0.034724444</v>
       </c>
     </row>
     <row r="95">
@@ -2050,13 +2050,13 @@
         <v>14</v>
       </c>
       <c r="C95" t="n">
-        <v>0.3213069</v>
+        <v>0.40488076</v>
       </c>
       <c r="D95" t="n">
         <v>0</v>
       </c>
       <c r="E95" t="n">
-        <v>-0.016363472</v>
+        <v>-0.03026852</v>
       </c>
     </row>
     <row r="96">
@@ -2067,13 +2067,13 @@
         <v>15</v>
       </c>
       <c r="C96" t="n">
-        <v>0.30494344</v>
+        <v>0.37461224</v>
       </c>
       <c r="D96" t="n">
         <v>0</v>
       </c>
       <c r="E96" t="n">
-        <v>-0.017308205</v>
+        <v>0.0035416186</v>
       </c>
     </row>
     <row r="97">
@@ -2084,13 +2084,13 @@
         <v>16</v>
       </c>
       <c r="C97" t="n">
-        <v>0.28763524</v>
+        <v>0.37815386</v>
       </c>
       <c r="D97" t="n">
         <v>0</v>
       </c>
       <c r="E97" t="n">
-        <v>0.015964538</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -2101,13 +2101,13 @@
         <v>17</v>
       </c>
       <c r="C98" t="n">
-        <v>0.30359977</v>
+        <v>0.37815386</v>
       </c>
       <c r="D98" t="n">
         <v>0</v>
       </c>
       <c r="E98" t="n">
-        <v>-0.015637815</v>
+        <v>0.004124433</v>
       </c>
     </row>
     <row r="99">
@@ -2118,13 +2118,13 @@
         <v>18</v>
       </c>
       <c r="C99" t="n">
-        <v>0.28796196</v>
+        <v>0.3822783</v>
       </c>
       <c r="D99" t="n">
         <v>0</v>
       </c>
       <c r="E99" t="n">
-        <v>0.0053997636</v>
+        <v>0.0008316636000000001</v>
       </c>
     </row>
     <row r="100">
@@ -2135,13 +2135,13 @@
         <v>19</v>
       </c>
       <c r="C100" t="n">
-        <v>0.29336172</v>
+        <v>0.38310996</v>
       </c>
       <c r="D100" t="n">
         <v>0</v>
       </c>
       <c r="E100" t="n">
-        <v>-0.0056792498</v>
+        <v>-0.021982938</v>
       </c>
     </row>
     <row r="101">
@@ -2152,13 +2152,13 @@
         <v>20</v>
       </c>
       <c r="C101" s="2" t="n">
-        <v>0.28768247</v>
+        <v>0.36112702</v>
       </c>
       <c r="D101" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>0.0070949793</v>
+        <v>-0.040640254</v>
       </c>
     </row>
     <row r="102">
@@ -2169,13 +2169,13 @@
         <v>1</v>
       </c>
       <c r="C102" t="n">
-        <v>0.29477745</v>
+        <v>0.37048677</v>
       </c>
       <c r="D102" t="n">
         <v>0</v>
       </c>
       <c r="E102" t="n">
-        <v>0.047075838</v>
+        <v>0.06208712</v>
       </c>
     </row>
     <row r="103">
@@ -2186,13 +2186,13 @@
         <v>2</v>
       </c>
       <c r="C103" t="n">
-        <v>0.3418533</v>
+        <v>0.43257388</v>
       </c>
       <c r="D103" t="n">
         <v>0</v>
       </c>
       <c r="E103" t="n">
-        <v>0.0065865815</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -2203,13 +2203,13 @@
         <v>3</v>
       </c>
       <c r="C104" t="n">
-        <v>0.34843987</v>
+        <v>0.43257388</v>
       </c>
       <c r="D104" t="n">
         <v>0</v>
       </c>
       <c r="E104" t="n">
-        <v>0.019955516</v>
+        <v>0.04585868</v>
       </c>
     </row>
     <row r="105">
@@ -2220,7 +2220,7 @@
         <v>4</v>
       </c>
       <c r="C105" t="n">
-        <v>0.3683954</v>
+        <v>0.47843257</v>
       </c>
       <c r="D105" t="n">
         <v>0</v>
@@ -2237,13 +2237,13 @@
         <v>5</v>
       </c>
       <c r="C106" t="n">
-        <v>0.3683954</v>
+        <v>0.47843257</v>
       </c>
       <c r="D106" t="n">
         <v>0</v>
       </c>
       <c r="E106" t="n">
-        <v>0.08513525</v>
+        <v>0.04617998</v>
       </c>
     </row>
     <row r="107">
@@ -2254,13 +2254,13 @@
         <v>6</v>
       </c>
       <c r="C107" t="n">
-        <v>0.45353064</v>
+        <v>0.52461255</v>
       </c>
       <c r="D107" t="n">
         <v>0</v>
       </c>
       <c r="E107" t="n">
-        <v>0.07852545399999999</v>
+        <v>0.075446784</v>
       </c>
     </row>
     <row r="108">
@@ -2271,13 +2271,13 @@
         <v>7</v>
       </c>
       <c r="C108" t="n">
-        <v>0.5320561</v>
+        <v>0.60005933</v>
       </c>
       <c r="D108" t="n">
         <v>0</v>
       </c>
       <c r="E108" t="n">
-        <v>-0.0028885603</v>
+        <v>0.0062406063</v>
       </c>
     </row>
     <row r="109">
@@ -2288,13 +2288,13 @@
         <v>8</v>
       </c>
       <c r="C109" t="n">
-        <v>0.5291675300000001</v>
+        <v>0.60629994</v>
       </c>
       <c r="D109" t="n">
         <v>0</v>
       </c>
       <c r="E109" t="n">
-        <v>-0.0013433099</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -2305,7 +2305,7 @@
         <v>9</v>
       </c>
       <c r="C110" t="n">
-        <v>0.5278242</v>
+        <v>0.60629994</v>
       </c>
       <c r="D110" t="n">
         <v>0</v>
@@ -2322,13 +2322,13 @@
         <v>10</v>
       </c>
       <c r="C111" t="n">
-        <v>0.5278242</v>
+        <v>0.60629994</v>
       </c>
       <c r="D111" t="n">
         <v>0</v>
       </c>
       <c r="E111" t="n">
-        <v>0.009927808999999999</v>
+        <v>0.008210421000000001</v>
       </c>
     </row>
     <row r="112">
@@ -2339,7 +2339,7 @@
         <v>11</v>
       </c>
       <c r="C112" t="n">
-        <v>0.53775203</v>
+        <v>0.61451036</v>
       </c>
       <c r="D112" t="n">
         <v>0</v>
@@ -2356,13 +2356,13 @@
         <v>12</v>
       </c>
       <c r="C113" t="n">
-        <v>0.53775203</v>
+        <v>0.61451036</v>
       </c>
       <c r="D113" t="n">
         <v>0</v>
       </c>
       <c r="E113" t="n">
-        <v>0.0028816462</v>
+        <v>0.0030950308</v>
       </c>
     </row>
     <row r="114">
@@ -2373,13 +2373,13 @@
         <v>13</v>
       </c>
       <c r="C114" t="n">
-        <v>0.5406337</v>
+        <v>0.6176054</v>
       </c>
       <c r="D114" t="n">
         <v>0</v>
       </c>
       <c r="E114" t="n">
-        <v>3.683567e-05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -2390,13 +2390,13 @@
         <v>14</v>
       </c>
       <c r="C115" t="n">
-        <v>0.5406705000000001</v>
+        <v>0.6176054</v>
       </c>
       <c r="D115" t="n">
         <v>0</v>
       </c>
       <c r="E115" t="n">
-        <v>0.0006045699</v>
+        <v>-0.0027378201</v>
       </c>
     </row>
     <row r="116">
@@ -2407,7 +2407,7 @@
         <v>15</v>
       </c>
       <c r="C116" t="n">
-        <v>0.5412751</v>
+        <v>0.61486757</v>
       </c>
       <c r="D116" t="n">
         <v>0</v>
@@ -2424,7 +2424,7 @@
         <v>16</v>
       </c>
       <c r="C117" t="n">
-        <v>0.5412751</v>
+        <v>0.61486757</v>
       </c>
       <c r="D117" t="n">
         <v>0</v>
@@ -2441,7 +2441,7 @@
         <v>17</v>
       </c>
       <c r="C118" t="n">
-        <v>0.5412751</v>
+        <v>0.61486757</v>
       </c>
       <c r="D118" t="n">
         <v>0</v>
@@ -2458,13 +2458,13 @@
         <v>18</v>
       </c>
       <c r="C119" t="n">
-        <v>0.5412751</v>
+        <v>0.61486757</v>
       </c>
       <c r="D119" t="n">
         <v>0</v>
       </c>
       <c r="E119" t="n">
-        <v>0.25363153</v>
+        <v>0.13887691</v>
       </c>
     </row>
     <row r="120">
@@ -2475,13 +2475,13 @@
         <v>19</v>
       </c>
       <c r="C120" s="2" t="n">
-        <v>0.7949066</v>
+        <v>0.7537445</v>
       </c>
       <c r="D120" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>0.005592108</v>
+        <v>-0.040657807</v>
       </c>
     </row>
     <row r="121">
@@ -2492,13 +2492,13 @@
         <v>1</v>
       </c>
       <c r="C121" t="n">
-        <v>0.8004987</v>
+        <v>0.7630867</v>
       </c>
       <c r="D121" t="n">
         <v>0</v>
       </c>
       <c r="E121" t="n">
-        <v>0.00715369</v>
+        <v>0.087747514</v>
       </c>
     </row>
     <row r="122">
@@ -2509,7 +2509,7 @@
         <v>2</v>
       </c>
       <c r="C122" t="n">
-        <v>0.8076524</v>
+        <v>0.8508342</v>
       </c>
       <c r="D122" t="n">
         <v>0</v>
@@ -2526,13 +2526,13 @@
         <v>3</v>
       </c>
       <c r="C123" t="n">
-        <v>0.8076524</v>
+        <v>0.8508342</v>
       </c>
       <c r="D123" t="n">
         <v>0</v>
       </c>
       <c r="E123" t="n">
-        <v>0</v>
+        <v>0.0040263534</v>
       </c>
     </row>
     <row r="124">
@@ -2543,13 +2543,13 @@
         <v>4</v>
       </c>
       <c r="C124" t="n">
-        <v>0.8076524</v>
+        <v>0.85486054</v>
       </c>
       <c r="D124" t="n">
         <v>0</v>
       </c>
       <c r="E124" t="n">
-        <v>-0.6183351</v>
+        <v>-0.6790299400000001</v>
       </c>
     </row>
     <row r="125">
@@ -2560,13 +2560,13 @@
         <v>5</v>
       </c>
       <c r="C125" t="n">
-        <v>0.1893173</v>
+        <v>0.17583057</v>
       </c>
       <c r="D125" t="n">
         <v>0</v>
       </c>
       <c r="E125" t="n">
-        <v>0.023961052</v>
+        <v>0.03233996</v>
       </c>
     </row>
     <row r="126">
@@ -2577,13 +2577,13 @@
         <v>6</v>
       </c>
       <c r="C126" t="n">
-        <v>0.21327835</v>
+        <v>0.20817053</v>
       </c>
       <c r="D126" t="n">
         <v>0</v>
       </c>
       <c r="E126" t="n">
-        <v>-0.022794202</v>
+        <v>-0.03227642</v>
       </c>
     </row>
     <row r="127">
@@ -2594,13 +2594,13 @@
         <v>7</v>
       </c>
       <c r="C127" t="n">
-        <v>0.19048415</v>
+        <v>0.17589411</v>
       </c>
       <c r="D127" t="n">
         <v>0</v>
       </c>
       <c r="E127" t="n">
-        <v>-0.009438068000000001</v>
+        <v>-0.0500852</v>
       </c>
     </row>
     <row r="128">
@@ -2611,13 +2611,13 @@
         <v>8</v>
       </c>
       <c r="C128" t="n">
-        <v>0.18104608</v>
+        <v>0.12580891</v>
       </c>
       <c r="D128" t="n">
         <v>0</v>
       </c>
       <c r="E128" t="n">
-        <v>-0.035971776</v>
+        <v>-0.04406122</v>
       </c>
     </row>
     <row r="129">
@@ -2628,13 +2628,13 @@
         <v>9</v>
       </c>
       <c r="C129" t="n">
-        <v>0.14507431</v>
+        <v>0.08174769</v>
       </c>
       <c r="D129" t="n">
         <v>0</v>
       </c>
       <c r="E129" t="n">
-        <v>0.0065505356</v>
+        <v>0.016021557</v>
       </c>
     </row>
     <row r="130">
@@ -2645,13 +2645,13 @@
         <v>10</v>
       </c>
       <c r="C130" t="n">
-        <v>0.15162484</v>
+        <v>0.097769246</v>
       </c>
       <c r="D130" t="n">
         <v>0</v>
       </c>
       <c r="E130" t="n">
-        <v>0.07181911000000001</v>
+        <v>0.20392765</v>
       </c>
     </row>
     <row r="131">
@@ -2662,13 +2662,13 @@
         <v>11</v>
       </c>
       <c r="C131" t="n">
-        <v>0.22344396</v>
+        <v>0.3016969</v>
       </c>
       <c r="D131" t="n">
         <v>0</v>
       </c>
       <c r="E131" t="n">
-        <v>-0.03856325</v>
+        <v>-0.089231715</v>
       </c>
     </row>
     <row r="132">
@@ -2679,13 +2679,13 @@
         <v>12</v>
       </c>
       <c r="C132" t="n">
-        <v>0.1848807</v>
+        <v>0.21246518</v>
       </c>
       <c r="D132" t="n">
         <v>0</v>
       </c>
       <c r="E132" t="n">
-        <v>-0.08147293999999999</v>
+        <v>-0.102129914</v>
       </c>
     </row>
     <row r="133">
@@ -2696,13 +2696,13 @@
         <v>13</v>
       </c>
       <c r="C133" t="n">
-        <v>0.10340776</v>
+        <v>0.11033527</v>
       </c>
       <c r="D133" t="n">
         <v>0</v>
       </c>
       <c r="E133" t="n">
-        <v>0.13480416</v>
+        <v>0.10736216</v>
       </c>
     </row>
     <row r="134">
@@ -2713,13 +2713,13 @@
         <v>14</v>
       </c>
       <c r="C134" t="n">
-        <v>0.23821191</v>
+        <v>0.21769743</v>
       </c>
       <c r="D134" t="n">
         <v>0</v>
       </c>
       <c r="E134" t="n">
-        <v>-0.043774873</v>
+        <v>-0.009634078000000001</v>
       </c>
     </row>
     <row r="135">
@@ -2730,13 +2730,13 @@
         <v>15</v>
       </c>
       <c r="C135" t="n">
-        <v>0.19443704</v>
+        <v>0.20806335</v>
       </c>
       <c r="D135" t="n">
         <v>0</v>
       </c>
       <c r="E135" t="n">
-        <v>0.0016589463</v>
+        <v>0.009103134000000001</v>
       </c>
     </row>
     <row r="136">
@@ -2747,13 +2747,13 @@
         <v>16</v>
       </c>
       <c r="C136" t="n">
-        <v>0.19609599</v>
+        <v>0.21716648</v>
       </c>
       <c r="D136" t="n">
         <v>0</v>
       </c>
       <c r="E136" t="n">
-        <v>0.06988214</v>
+        <v>0.12025359</v>
       </c>
     </row>
     <row r="137">
@@ -2764,13 +2764,13 @@
         <v>17</v>
       </c>
       <c r="C137" t="n">
-        <v>0.26597813</v>
+        <v>0.33742008</v>
       </c>
       <c r="D137" t="n">
         <v>0</v>
       </c>
       <c r="E137" t="n">
-        <v>0.26757076</v>
+        <v>0.3427703</v>
       </c>
     </row>
     <row r="138">
@@ -2781,47 +2781,47 @@
         <v>18</v>
       </c>
       <c r="C138" t="n">
-        <v>0.5335489</v>
+        <v>0.6801904</v>
       </c>
       <c r="D138" t="n">
         <v>0</v>
       </c>
       <c r="E138" t="n">
-        <v>0.1641227</v>
+        <v>0.08013242499999999</v>
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="n">
+      <c r="A139" s="2" t="n">
         <v>138</v>
       </c>
-      <c r="B139" t="n">
+      <c r="B139" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="C139" t="n">
-        <v>0.6976715999999999</v>
-      </c>
-      <c r="D139" t="n">
-        <v>0</v>
-      </c>
-      <c r="E139" t="n">
-        <v>-0.0062034726</v>
+      <c r="C139" s="2" t="n">
+        <v>0.7603228</v>
+      </c>
+      <c r="D139" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E139" s="2" t="n">
+        <v>0.012514722</v>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="n">
+      <c r="A140" t="n">
         <v>139</v>
       </c>
-      <c r="B140" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="C140" s="2" t="n">
-        <v>0.6914681</v>
-      </c>
-      <c r="D140" s="2" t="n">
+      <c r="B140" t="n">
         <v>1</v>
       </c>
-      <c r="E140" s="2" t="n">
-        <v>-0.0038192272</v>
+      <c r="C140" t="n">
+        <v>0.82283753</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0</v>
+      </c>
+      <c r="E140" t="n">
+        <v>-0.06630039</v>
       </c>
     </row>
     <row r="141">
@@ -2829,16 +2829,16 @@
         <v>140</v>
       </c>
       <c r="B141" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C141" t="n">
-        <v>0.6876489</v>
+        <v>0.7565371400000001</v>
       </c>
       <c r="D141" t="n">
         <v>0</v>
       </c>
       <c r="E141" t="n">
-        <v>0.0424577</v>
+        <v>0.06881845</v>
       </c>
     </row>
     <row r="142">
@@ -2846,16 +2846,16 @@
         <v>141</v>
       </c>
       <c r="B142" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C142" t="n">
-        <v>0.7301066</v>
+        <v>0.8253556</v>
       </c>
       <c r="D142" t="n">
         <v>0</v>
       </c>
       <c r="E142" t="n">
-        <v>0.020862222</v>
+        <v>-0.013350189</v>
       </c>
     </row>
     <row r="143">
@@ -2863,16 +2863,16 @@
         <v>142</v>
       </c>
       <c r="B143" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C143" t="n">
-        <v>0.7509688</v>
+        <v>0.8120054</v>
       </c>
       <c r="D143" t="n">
         <v>0</v>
       </c>
       <c r="E143" t="n">
-        <v>0.061309695</v>
+        <v>0.034856975</v>
       </c>
     </row>
     <row r="144">
@@ -2880,16 +2880,16 @@
         <v>143</v>
       </c>
       <c r="B144" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C144" t="n">
-        <v>0.8122785</v>
+        <v>0.8468624</v>
       </c>
       <c r="D144" t="n">
         <v>0</v>
       </c>
       <c r="E144" t="n">
-        <v>-0.0051422715</v>
+        <v>0.0018770695</v>
       </c>
     </row>
     <row r="145">
@@ -2897,16 +2897,16 @@
         <v>144</v>
       </c>
       <c r="B145" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C145" t="n">
-        <v>0.8071362399999999</v>
+        <v>0.84873945</v>
       </c>
       <c r="D145" t="n">
         <v>0</v>
       </c>
       <c r="E145" t="n">
-        <v>0.02189678</v>
+        <v>0.004532695</v>
       </c>
     </row>
     <row r="146">
@@ -2914,16 +2914,16 @@
         <v>145</v>
       </c>
       <c r="B146" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C146" t="n">
-        <v>0.829033</v>
+        <v>0.85327214</v>
       </c>
       <c r="D146" t="n">
         <v>0</v>
       </c>
       <c r="E146" t="n">
-        <v>-0.0048542023</v>
+        <v>-0.010417581</v>
       </c>
     </row>
     <row r="147">
@@ -2931,16 +2931,16 @@
         <v>146</v>
       </c>
       <c r="B147" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C147" t="n">
-        <v>0.8241788</v>
+        <v>0.84285456</v>
       </c>
       <c r="D147" t="n">
         <v>0</v>
       </c>
       <c r="E147" t="n">
-        <v>0</v>
+        <v>0.0027078986</v>
       </c>
     </row>
     <row r="148">
@@ -2948,16 +2948,16 @@
         <v>147</v>
       </c>
       <c r="B148" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C148" t="n">
-        <v>0.8241788</v>
+        <v>0.84556246</v>
       </c>
       <c r="D148" t="n">
         <v>0</v>
       </c>
       <c r="E148" t="n">
-        <v>0.03817773</v>
+        <v>0.0013126731</v>
       </c>
     </row>
     <row r="149">
@@ -2965,16 +2965,16 @@
         <v>148</v>
       </c>
       <c r="B149" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C149" t="n">
-        <v>0.8623565399999999</v>
+        <v>0.84687513</v>
       </c>
       <c r="D149" t="n">
         <v>0</v>
       </c>
       <c r="E149" t="n">
-        <v>0.006299317</v>
+        <v>0.017712414</v>
       </c>
     </row>
     <row r="150">
@@ -2982,16 +2982,16 @@
         <v>149</v>
       </c>
       <c r="B150" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C150" t="n">
-        <v>0.8686558599999999</v>
+        <v>0.86458755</v>
       </c>
       <c r="D150" t="n">
         <v>0</v>
       </c>
       <c r="E150" t="n">
-        <v>-0.0012839437</v>
+        <v>0.00027751923</v>
       </c>
     </row>
   </sheetData>
